--- a/data/trans_camb/IP18A05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,0</t>
+          <t>-7,36; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 0,0</t>
+          <t>-7,23; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 22,45</t>
+          <t>-2,87; 25,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,0</t>
+          <t>-4,01; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,0</t>
+          <t>-2,9; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 10,24</t>
+          <t>-1,41; 10,13</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 11,1</t>
+          <t>2,09; 10,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,42</t>
+          <t>0,0; 22,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,82</t>
+          <t>0,0; 34,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,67</t>
+          <t>2,81; 8,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 18,64</t>
+          <t>1,35; 19,69</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,72</t>
+          <t>0,0; 6,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,7</t>
+          <t>0,0; 23,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,9</t>
+          <t>0,92; 8,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,01</t>
+          <t>0,49; 4,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,68</t>
+          <t>0,0; 11,83</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 0,0</t>
+          <t>-7,35; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,56</t>
+          <t>-5,22; 1,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 0,0</t>
+          <t>-5,82; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,19</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,1</t>
+          <t>-2,57; 1,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,74</t>
+          <t>-2,55; 0,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,0</t>
+          <t>-3,53; 0,0</t>
         </is>
       </c>
     </row>
@@ -1556,32 +1556,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 0,0</t>
+          <t>-17,31; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 0,0</t>
+          <t>-14,46; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 40,8</t>
+          <t>-5,91; 41,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 0,0</t>
+          <t>-7,45; 0,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 0,0</t>
+          <t>-9,01; 0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 26,16</t>
+          <t>-3,0; 29,46</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,58</t>
+          <t>0,0; 9,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,27; 12,06</t>
+          <t>1,25; 12,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,17</t>
+          <t>1,35; 8,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,15</t>
+          <t>-1,3; 2,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 5,03</t>
+          <t>-0,53; 4,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 15,97</t>
+          <t>-1,17; 15,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,27; 8,77</t>
+          <t>0,98; 8,39</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,24; 27,82</t>
+          <t>2,22; 29,54</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,46</t>
+          <t>-0,58; 1,51</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,4</t>
+          <t>1,05; 5,5</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,44; 17,94</t>
+          <t>1,8; 17,17</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,56</t>
+          <t>-2,82; 1,53</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,0</t>
+          <t>-3,83; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,0</t>
+          <t>-4,63; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,82</t>
+          <t>-3,95; 0,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,43; -0,52</t>
+          <t>-4,87; -0,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 14,26</t>
+          <t>-2,58; 18,42</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,69</t>
+          <t>-2,31; 0,71</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,12; -0,53</t>
+          <t>-3,36; -0,54</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 9,39</t>
+          <t>-1,87; 10,44</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 219,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-89,27; 157,06</t>
+          <t>-89,98; 158,07</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,02</t>
+          <t>-0,64; 1,02</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,48</t>
+          <t>-0,3; 1,43</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,27; 6,35</t>
+          <t>0,21; 5,72</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,46</t>
+          <t>-0,23; 1,42</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,94</t>
+          <t>0,03; 1,86</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,37; 9,37</t>
+          <t>1,1; 8,53</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,98</t>
+          <t>-0,21; 0,97</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,36</t>
+          <t>0,06; 1,37</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,87</t>
+          <t>1,29; 5,97</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-64,21; 378,1</t>
+          <t>-64,24; 345,79</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 642,13</t>
+          <t>-48,2; 507,61</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 2083,33</t>
+          <t>-22,09; 1973,84</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 697,45</t>
+          <t>-43,28; 626,39</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 732,12</t>
+          <t>-20,18; 801,19</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>77,9; 3292,96</t>
+          <t>77,55; 2683,06</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 297,86</t>
+          <t>-25,52; 256,65</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 386,27</t>
+          <t>-3,21; 337,73</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>141,78; 1424,17</t>
+          <t>138,86; 1518,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Provincia-trans_camb.xlsx
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 0,0</t>
+          <t>-8,13; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,0</t>
+          <t>-8,32; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 25,86</t>
+          <t>-2,88; 22,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,0</t>
+          <t>-3,57; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,0</t>
+          <t>-3,16; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 10,13</t>
+          <t>-1,41; 10,33</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 10,6</t>
+          <t>2,12; 10,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,04</t>
+          <t>0,0; 20,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -913,27 +913,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,12</t>
+          <t>2,09; 10,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,78</t>
+          <t>0,0; 31,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,45</t>
+          <t>2,31; 7,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 19,69</t>
+          <t>1,34; 17,82</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,07</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,34</t>
+          <t>0,0; 22,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,69</t>
+          <t>0,91; 7,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,6</t>
+          <t>0,54; 4,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,83</t>
+          <t>0,0; 10,64</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,0</t>
+          <t>-6,4; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 1,57</t>
+          <t>-5,15; 1,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,0</t>
+          <t>-6,44; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,09</t>
+          <t>-2,02; 1,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,74</t>
+          <t>-2,25; 0,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,0</t>
+          <t>-3,25; 0,0</t>
         </is>
       </c>
     </row>
@@ -1556,32 +1556,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 0,0</t>
+          <t>-14,47; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 0,0</t>
+          <t>-14,49; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 41,87</t>
+          <t>-5,95; 41,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 0,0</t>
+          <t>-7,44; 0,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 0,0</t>
+          <t>-9,17; 0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 29,46</t>
+          <t>-1,54; 30,02</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>0,0; 9,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,25; 12,15</t>
+          <t>1,26; 12,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,4</t>
+          <t>1,31; 8,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,43</t>
+          <t>-1,75; 2,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,81</t>
+          <t>-0,2; 4,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 15,25</t>
+          <t>-1,17; 17,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,39</t>
+          <t>1,35; 8,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,22; 29,54</t>
+          <t>2,3; 30,23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,51</t>
+          <t>-0,58; 1,52</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,5</t>
+          <t>1,0; 5,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,8; 17,17</t>
+          <t>1,75; 21,16</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,53</t>
+          <t>-2,44; 1,57</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,0</t>
+          <t>-3,75; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,0</t>
+          <t>-3,99; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,74</t>
+          <t>-4,05; 0,77</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,87; -0,52</t>
+          <t>-4,9; -0,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 18,42</t>
+          <t>-2,61; 16,26</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,71</t>
+          <t>-2,64; 0,58</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,54</t>
+          <t>-3,35; -0,73</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 10,44</t>
+          <t>-2,01; 9,88</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-89,98; 158,07</t>
+          <t>-100,0; 111,52</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,02</t>
+          <t>-0,64; 1,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,43</t>
+          <t>-0,26; 1,51</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,72</t>
+          <t>0,31; 5,92</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,42</t>
+          <t>-0,28; 1,4</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,86</t>
+          <t>-0,1; 1,8</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,53</t>
+          <t>1,2; 8,48</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,97</t>
+          <t>-0,18; 0,96</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,37</t>
+          <t>0,07; 1,4</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,97</t>
+          <t>1,24; 5,61</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-64,24; 345,79</t>
+          <t>-70,37; 416,36</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 507,61</t>
+          <t>-39,25; 664,98</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 1973,84</t>
+          <t>-27,18; 1789,85</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-43,28; 626,39</t>
+          <t>-42,58; 602,17</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 801,19</t>
+          <t>-28,23; 698,18</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>77,55; 2683,06</t>
+          <t>92,77; 2998,07</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 256,65</t>
+          <t>-26,17; 291,77</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 337,73</t>
+          <t>2,41; 499,06</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>138,86; 1518,28</t>
+          <t>145,15; 1477,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>1,76</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 22,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,29; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,26; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,87; 21,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 0,0</t>
+          <t>-3,6; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,0</t>
+          <t>-3,59; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 10,33</t>
+          <t>-1,43; 10,16</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>271,92%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>257,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>249,94%</t>
+          <t>247,0%</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,89</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,11</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,69</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,93</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,05</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,89</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>6,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 10,35</t>
+          <t>1,76; 10,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,5</t>
+          <t>0,0; 37,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 10,34</t>
+          <t>2,11; 11,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,52</t>
+          <t>0,0; 16,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,95</t>
+          <t>2,65; 8,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 17,82</t>
+          <t>1,14; 20,02</t>
         </is>
       </c>
     </row>
@@ -946,22 +946,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,09</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,94</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>3,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,92; 7,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,88</t>
+          <t>0,0; 7,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,77</t>
+          <t>0,54; 5,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,64</t>
+          <t>0,0; 10,74</t>
         </is>
       </c>
     </row>
@@ -1167,27 +1167,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,04</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-1,29</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,0</t>
+          <t>0,0; 5,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 1,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>-7,4; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,1; 1,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,48; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,12</t>
+          <t>-2,05; 1,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,74</t>
+          <t>-2,61; 0,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,0</t>
+          <t>-3,21; 0,0</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-40,01%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1488,34 +1488,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,99</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,99</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7,43</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7,71</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>-1,51</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>4,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,49; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,23; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,93; 40,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 41,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 0,0</t>
+          <t>-7,47; 0,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 0,0</t>
+          <t>-6,06; 0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 30,02</t>
+          <t>-3,01; 24,62</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>248,76%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>258,12%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>306,57%</t>
+          <t>285,22%</t>
         </is>
       </c>
     </row>
@@ -1704,22 +1704,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>5,0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,74</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5,0</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,44</t>
+          <t>1,27; 12,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,26; 12,03</t>
+          <t>0,0; 9,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,31; 8,18</t>
+          <t>1,87; 8,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3,81</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>10,86</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,45</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,71</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,95</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,75</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>7,85</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,13</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4,99</t>
+          <t>1,27; 8,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 17,1</t>
+          <t>1,93; 28,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>-1,3; 2,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,78</t>
+          <t>-0,49; 5,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,3; 30,23</t>
+          <t>-1,16; 21,1</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,52</t>
+          <t>-0,58; 1,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,34</t>
+          <t>1,26; 5,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,75; 21,16</t>
+          <t>1,58; 19,8</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>76,28%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>292,87%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>504,91%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>641,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2502,88%</t>
+          <t>2711,82%</t>
         </is>
       </c>
     </row>
@@ -2136,34 +2136,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-1,92</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-0,23</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-1,15</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-1,15</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>-0,68</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,44</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,57</t>
+          <t>-3,45; 0,82</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,0</t>
+          <t>-4,43; -0,52</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,0</t>
+          <t>-2,6; 13,12</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,77</t>
+          <t>-2,69; 1,56</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -0,52</t>
+          <t>-3,94; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 16,26</t>
+          <t>-4,36; 0,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,58</t>
+          <t>-2,36; 0,69</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,73</t>
+          <t>-3,12; -0,53</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 9,88</t>
+          <t>-2,02; 8,39</t>
         </is>
       </c>
     </row>
@@ -2242,47 +2242,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-56,64%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>65,18%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-19,91%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-56,64%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-43,64%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>84,67%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-43,64%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 219,94</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 111,52</t>
+          <t>-89,27; 157,06</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,86</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>3,96</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,23</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>0,54</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>3,21</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,03</t>
+          <t>-0,18; 1,46</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,51</t>
+          <t>-0,04; 1,94</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,92</t>
+          <t>1,42; 10,06</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,4</t>
+          <t>-0,65; 1,02</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,8</t>
+          <t>-0,25; 1,48</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,48</t>
+          <t>0,29; 6,75</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,96</t>
+          <t>-0,24; 0,98</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,4</t>
+          <t>0,08; 1,36</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,61</t>
+          <t>1,4; 6,15</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>151,78%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>701,86%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>36,36%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>86,94%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>365,61%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>151,78%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>669,03%</t>
+          <t>363,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>527,48%</t>
+          <t>542,17%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 416,36</t>
+          <t>-32,26; 697,45</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 664,98</t>
+          <t>-24,92; 732,12</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 1789,85</t>
+          <t>88,0; 3811,2</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-42,58; 602,17</t>
+          <t>-64,21; 378,1</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 698,18</t>
+          <t>-45,36; 642,13</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>92,77; 2998,07</t>
+          <t>-25,93; 2111,86</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 291,77</t>
+          <t>-31,19; 297,86</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,41; 499,06</t>
+          <t>-1,76; 386,27</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>145,15; 1477,68</t>
+          <t>145,17; 1492,17</t>
         </is>
       </c>
     </row>
